--- a/data/pack/eu/avena.xlsx
+++ b/data/pack/eu/avena.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1039,6 +1039,61 @@
         </is>
       </c>
       <c r="K11" t="inlineStr">
+        <is>
+          <t>Source: European Commission (Agri-food data portal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>avena</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Avena</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>124.71</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>tonelada</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>European Commission — Agri-food Data Portal (DG AGRI)</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>EU-REUSE-2011-833</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>Source: European Commission (Agri-food data portal)</t>
         </is>
@@ -1142,7 +1197,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1208,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
@@ -1248,7 +1303,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>

--- a/data/pack/eu/avena.xlsx
+++ b/data/pack/eu/avena.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1094,6 +1094,61 @@
         </is>
       </c>
       <c r="K12" t="inlineStr">
+        <is>
+          <t>Source: European Commission (Agri-food data portal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>avena</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Avena</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>131.04</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>tonelada</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>European Commission — Agri-food Data Portal (DG AGRI)</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>EU-REUSE-2011-833</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>Source: European Commission (Agri-food data portal)</t>
         </is>
@@ -1197,7 +1252,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1263,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -1303,7 +1358,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
